--- a/codebooks/c_educacion/2024_adopcion_digital.xlsx
+++ b/codebooks/c_educacion/2024_adopcion_digital.xlsx
@@ -210,6 +210,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -483,7 +487,7 @@
     <col min="6" max="6" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="174" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -503,7 +507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="174" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -523,7 +527,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="174" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -543,7 +547,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="174" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -563,7 +567,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="174" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -583,7 +587,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="174" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
@@ -603,7 +607,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="174" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
